--- a/tiflow/develop/2.0.0-ballot.1/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/CodeSystem/tiflow-operation-outcome-details-cs</t>
+    <t>https://gematik.de/fhir/tiflow/CodeSystem/tiflow-operation-outcome-details-cs</t>
   </si>
   <si>
     <t>Version</t>

--- a/tiflow/develop/2.0.0-ballot.1/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>40</t>
+    <t>41</t>
   </si>
   <si>
     <t>Level</t>
@@ -502,6 +502,15 @@
   </si>
   <si>
     <t>Failed to retrieve the OCSP response for the certificate of the signature</t>
+  </si>
+  <si>
+    <t>TIFLOW_POPP_TOKEN_INVALID</t>
+  </si>
+  <si>
+    <t>Invalid PoPP token</t>
+  </si>
+  <si>
+    <t>The provided PoPP token is invalid</t>
   </si>
 </sst>
 </file>
@@ -813,7 +822,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1390,6 +1399,20 @@
         <v>162</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/tiflow/develop/2.0.0-ballot.1/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/CodeSystem-tiflow-operation-outcome-details-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="172">
   <si>
     <t>Property</t>
   </si>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>41</t>
+    <t>43</t>
   </si>
   <si>
     <t>Level</t>
@@ -511,6 +511,24 @@
   </si>
   <si>
     <t>The provided PoPP token is invalid</t>
+  </si>
+  <si>
+    <t>TIFLOW_TIMEOUT</t>
+  </si>
+  <si>
+    <t>Timeout</t>
+  </si>
+  <si>
+    <t>The service took to long to process the request and cancelled it.</t>
+  </si>
+  <si>
+    <t>TIFLOW_INTERNAL_ERROR</t>
+  </si>
+  <si>
+    <t>Internal Server Error</t>
+  </si>
+  <si>
+    <t>The service ran into an unspecified error.</t>
   </si>
 </sst>
 </file>
@@ -822,7 +840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1413,6 +1431,34 @@
         <v>165</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="D43" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="D44" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
